--- a/panchang-data/Toronto2026.xlsx
+++ b/panchang-data/Toronto2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5424">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16297,6 +16297,9 @@
   </si>
   <si>
     <t>121°03'33.00</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16786,7 +16789,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16872,7 +16875,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>52</v>
@@ -16958,7 +16961,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>73</v>
@@ -17044,7 +17047,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
@@ -17130,7 +17133,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>109</v>
@@ -17216,7 +17219,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>127</v>
@@ -17302,7 +17305,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>145</v>
@@ -17388,7 +17391,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17474,7 +17477,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>52</v>
@@ -17560,7 +17563,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>73</v>
@@ -17646,7 +17649,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>92</v>
@@ -17732,7 +17735,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>109</v>
@@ -17818,7 +17821,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>127</v>
@@ -17904,7 +17907,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>145</v>
@@ -17990,7 +17993,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18076,7 +18079,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>52</v>
@@ -18162,7 +18165,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>73</v>
@@ -18248,7 +18251,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>92</v>
@@ -18334,7 +18337,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>109</v>
@@ -18420,7 +18423,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>127</v>
@@ -18506,7 +18509,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>145</v>
@@ -18592,7 +18595,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18678,7 +18681,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>52</v>
@@ -18764,7 +18767,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>73</v>
@@ -18850,7 +18853,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>92</v>
@@ -18936,7 +18939,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>109</v>
@@ -19022,7 +19025,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>127</v>
@@ -19108,7 +19111,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>145</v>
@@ -19194,7 +19197,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19280,7 +19283,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>52</v>
@@ -19366,7 +19369,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>73</v>
@@ -19452,7 +19455,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>72</v>
+        <v>571</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>92</v>
@@ -19538,7 +19541,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>109</v>
@@ -19624,7 +19627,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>127</v>
@@ -19710,7 +19713,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>145</v>
@@ -19796,7 +19799,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19882,7 +19885,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>52</v>
@@ -19968,7 +19971,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>73</v>
@@ -20054,7 +20057,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>92</v>
@@ -20140,7 +20143,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>109</v>
@@ -20226,7 +20229,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>127</v>
@@ -20312,7 +20315,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>145</v>
@@ -20398,7 +20401,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20484,7 +20487,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>52</v>
@@ -20570,7 +20573,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>73</v>
@@ -20656,7 +20659,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>92</v>
@@ -20742,7 +20745,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>109</v>
@@ -20828,7 +20831,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>127</v>
@@ -20914,7 +20917,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>145</v>
@@ -21000,7 +21003,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21086,7 +21089,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>52</v>
@@ -21172,7 +21175,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>73</v>
@@ -21258,7 +21261,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>92</v>
@@ -21344,7 +21347,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>109</v>
@@ -21430,7 +21433,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>127</v>
@@ -21516,7 +21519,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>145</v>
@@ -21602,7 +21605,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21688,7 +21691,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>52</v>
@@ -21774,7 +21777,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>73</v>
@@ -21860,7 +21863,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>92</v>
@@ -21946,7 +21949,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>571</v>
+        <v>999</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>109</v>
@@ -22032,7 +22035,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>127</v>
@@ -22118,7 +22121,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>145</v>
@@ -22204,7 +22207,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22290,7 +22293,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>52</v>
@@ -22376,7 +22379,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>73</v>
@@ -22462,7 +22465,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>92</v>
@@ -22548,7 +22551,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>109</v>
@@ -22634,7 +22637,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>127</v>
@@ -22720,7 +22723,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>145</v>
@@ -22806,7 +22809,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22892,7 +22895,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>52</v>
@@ -22978,7 +22981,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>73</v>
@@ -23064,7 +23067,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>92</v>
@@ -23150,7 +23153,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>109</v>
@@ -23236,7 +23239,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>127</v>
@@ -23322,7 +23325,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>145</v>
@@ -23408,7 +23411,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23494,7 +23497,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>52</v>
@@ -23580,7 +23583,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>73</v>
@@ -23666,7 +23669,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>92</v>
@@ -23752,7 +23755,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>109</v>
@@ -23838,7 +23841,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>127</v>
@@ -23924,7 +23927,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>145</v>
@@ -24010,7 +24013,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24096,7 +24099,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>52</v>
@@ -24182,7 +24185,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>73</v>
@@ -24268,7 +24271,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>92</v>
@@ -24354,7 +24357,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>109</v>
@@ -24440,7 +24443,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>127</v>
@@ -24526,7 +24529,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>999</v>
+        <v>1440</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>145</v>
@@ -24612,7 +24615,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24698,7 +24701,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>52</v>
@@ -24784,7 +24787,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>73</v>
@@ -24870,7 +24873,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>92</v>
@@ -24956,7 +24959,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>109</v>
@@ -25042,7 +25045,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>127</v>
@@ -25128,7 +25131,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>145</v>
@@ -25214,7 +25217,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25300,7 +25303,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>52</v>
@@ -25386,7 +25389,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>73</v>
@@ -25472,7 +25475,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>92</v>
@@ -25558,7 +25561,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>109</v>
@@ -25644,7 +25647,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>127</v>
@@ -25730,7 +25733,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>145</v>
@@ -25816,7 +25819,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25902,7 +25905,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>52</v>
@@ -25988,7 +25991,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>73</v>
@@ -26074,7 +26077,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>92</v>
@@ -26160,7 +26163,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>109</v>
@@ -26246,7 +26249,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>127</v>
@@ -26332,7 +26335,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>145</v>
@@ -26418,7 +26421,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26504,7 +26507,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>52</v>
@@ -26590,7 +26593,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>73</v>
@@ -26676,7 +26679,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>92</v>
@@ -26762,7 +26765,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>109</v>
@@ -26848,7 +26851,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>127</v>
@@ -26934,7 +26937,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>145</v>
@@ -27020,7 +27023,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27106,7 +27109,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1440</v>
+        <v>1878</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>52</v>
@@ -27192,7 +27195,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>73</v>
@@ -27278,7 +27281,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>92</v>
@@ -27364,7 +27367,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>109</v>
@@ -27450,7 +27453,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>127</v>
@@ -27536,7 +27539,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>145</v>
@@ -27622,7 +27625,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27708,7 +27711,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>52</v>
@@ -27794,7 +27797,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>73</v>
@@ -27880,7 +27883,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>92</v>
@@ -27966,7 +27969,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>109</v>
@@ -28052,7 +28055,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>127</v>
@@ -28138,7 +28141,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>145</v>
@@ -28224,7 +28227,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28310,7 +28313,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>52</v>
@@ -28396,7 +28399,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1878</v>
+        <v>2300</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>73</v>
@@ -28482,7 +28485,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>92</v>
@@ -28568,7 +28571,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>109</v>
@@ -28654,7 +28657,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>127</v>
@@ -28740,7 +28743,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>145</v>
@@ -28826,7 +28829,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28912,7 +28915,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>52</v>
@@ -28998,7 +29001,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>73</v>
@@ -29084,7 +29087,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>92</v>
@@ -29170,7 +29173,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>109</v>
@@ -29256,7 +29259,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>127</v>
@@ -29342,7 +29345,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>145</v>
@@ -29428,7 +29431,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29514,7 +29517,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>52</v>
@@ -29600,7 +29603,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1878</v>
+        <v>5423</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>73</v>
@@ -29686,7 +29689,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>92</v>
@@ -29772,7 +29775,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>109</v>
@@ -29858,7 +29861,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>127</v>
@@ -29944,7 +29947,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>145</v>
@@ -30030,7 +30033,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30116,7 +30119,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>52</v>
@@ -30202,7 +30205,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>73</v>
@@ -30288,7 +30291,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>92</v>
@@ -30374,7 +30377,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>109</v>
@@ -30460,7 +30463,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>127</v>
@@ -30546,7 +30549,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>145</v>
@@ -30632,7 +30635,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30718,7 +30721,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>52</v>
@@ -30804,7 +30807,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>73</v>
@@ -30890,7 +30893,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2300</v>
+        <v>5423</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>92</v>
